--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:17:07+00:00</t>
+    <t>2023-02-20T03:26:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2210" uniqueCount="467">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T03:26:30+00:00</t>
+    <t>2023-02-20T22:25:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -432,14 +432,11 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>ExtBoolMedioNotificacion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ExtBoolMedioNotificacion}
+    <t>MedioNotificacion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/MedioNotificacion}
 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ExtBool Medio Notificacion </t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -449,11 +446,11 @@
     <t>ContactadoLE</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/ContactadoLE}
+    <t xml:space="preserve">Extension {http://minsal.cl/listaespera/StructureDefinition/Contactado}
 </t>
   </si>
   <si>
-    <t>Contacto del paciente</t>
+    <t>Contactado</t>
   </si>
   <si>
     <t>Appointment.modifierExtension</t>
@@ -1780,7 +1777,7 @@
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="49.0078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="24.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.35546875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="6.77734375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2877,10 +2874,10 @@
         <v>135</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
@@ -2940,7 +2937,7 @@
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>133</v>
@@ -2966,7 +2963,7 @@
         <v>126</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C11" t="s" s="2">
         <v>73</v>
@@ -2988,13 +2985,13 @@
         <v>73</v>
       </c>
       <c r="J11" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="K11" t="s" s="2">
         <v>139</v>
       </c>
-      <c r="K11" t="s" s="2">
-        <v>140</v>
-      </c>
       <c r="L11" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
@@ -3054,7 +3051,7 @@
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>133</v>
@@ -3077,11 +3074,11 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B12" s="2"/>
       <c r="C12" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" t="s" s="2">
@@ -3103,16 +3100,16 @@
         <v>127</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>143</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>144</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O12" t="s" s="2">
         <v>73</v>
@@ -3161,7 +3158,7 @@
         <v>73</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AF12" t="s" s="2">
         <v>74</v>
@@ -3193,7 +3190,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2"/>
       <c r="C13" t="s" s="2">
@@ -3216,13 +3213,13 @@
         <v>83</v>
       </c>
       <c r="J13" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="K13" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="K13" t="s" s="2">
+      <c r="L13" t="s" s="2">
         <v>150</v>
-      </c>
-      <c r="L13" t="s" s="2">
-        <v>151</v>
       </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
@@ -3273,7 +3270,7 @@
         <v>73</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AF13" t="s" s="2">
         <v>74</v>
@@ -3288,24 +3285,24 @@
         <v>94</v>
       </c>
       <c r="AJ13" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AK13" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="AK13" t="s" s="2">
+      <c r="AL13" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AM13" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B14" s="2"/>
       <c r="C14" t="s" s="2">
@@ -3328,13 +3325,13 @@
         <v>73</v>
       </c>
       <c r="J14" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K14" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K14" t="s" s="2">
+      <c r="L14" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L14" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -3385,7 +3382,7 @@
         <v>73</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF14" t="s" s="2">
         <v>74</v>
@@ -3403,7 +3400,7 @@
         <v>73</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>73</v>
@@ -3417,11 +3414,11 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B15" s="2"/>
       <c r="C15" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" t="s" s="2">
@@ -3443,13 +3440,13 @@
         <v>127</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L15" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M15" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" t="s" s="2">
@@ -3490,7 +3487,7 @@
         <v>130</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC15" t="s" s="2">
         <v>73</v>
@@ -3499,7 +3496,7 @@
         <v>131</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>74</v>
@@ -3517,7 +3514,7 @@
         <v>73</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>73</v>
@@ -3531,7 +3528,7 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" t="s" s="2">
@@ -3557,16 +3554,16 @@
         <v>102</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>169</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O16" t="s" s="2">
         <v>73</v>
@@ -3591,31 +3588,31 @@
         <v>73</v>
       </c>
       <c r="W16" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="X16" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="X16" t="s" s="2">
+      <c r="Y16" t="s" s="2">
         <v>174</v>
       </c>
-      <c r="Y16" t="s" s="2">
+      <c r="Z16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD16" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE16" t="s" s="2">
         <v>175</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>176</v>
       </c>
       <c r="AF16" t="s" s="2">
         <v>74</v>
@@ -3633,7 +3630,7 @@
         <v>73</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>73</v>
@@ -3647,7 +3644,7 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B17" s="2"/>
       <c r="C17" t="s" s="2">
@@ -3670,19 +3667,19 @@
         <v>83</v>
       </c>
       <c r="J17" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="K17" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="K17" t="s" s="2">
+      <c r="L17" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>181</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>182</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="O17" t="s" s="2">
         <v>73</v>
@@ -3707,31 +3704,31 @@
         <v>73</v>
       </c>
       <c r="W17" t="s" s="2">
+        <v>183</v>
+      </c>
+      <c r="X17" t="s" s="2">
         <v>184</v>
       </c>
-      <c r="X17" t="s" s="2">
+      <c r="Y17" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="Y17" t="s" s="2">
+      <c r="Z17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD17" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE17" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="Z17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD17" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE17" t="s" s="2">
-        <v>187</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>74</v>
@@ -3749,7 +3746,7 @@
         <v>73</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>73</v>
@@ -3758,12 +3755,12 @@
         <v>73</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B18" s="2"/>
       <c r="C18" t="s" s="2">
@@ -3789,16 +3786,16 @@
         <v>96</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="L18" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="M18" t="s" s="2">
         <v>191</v>
       </c>
-      <c r="M18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>192</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="O18" t="s" s="2">
         <v>73</v>
@@ -3811,43 +3808,43 @@
         <v>73</v>
       </c>
       <c r="S18" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="T18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE18" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="T18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE18" t="s" s="2">
-        <v>195</v>
       </c>
       <c r="AF18" t="s" s="2">
         <v>74</v>
@@ -3865,21 +3862,21 @@
         <v>73</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>195</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>196</v>
-      </c>
-      <c r="AL18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM18" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>197</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B19" s="2"/>
       <c r="C19" t="s" s="2">
@@ -3902,16 +3899,16 @@
         <v>83</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>199</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
@@ -3925,43 +3922,43 @@
         <v>73</v>
       </c>
       <c r="S19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="T19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE19" t="s" s="2">
         <v>202</v>
-      </c>
-      <c r="T19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE19" t="s" s="2">
-        <v>203</v>
       </c>
       <c r="AF19" t="s" s="2">
         <v>74</v>
@@ -3979,21 +3976,21 @@
         <v>73</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM19" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>204</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>205</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B20" s="2"/>
       <c r="C20" t="s" s="2">
@@ -4016,13 +4013,13 @@
         <v>83</v>
       </c>
       <c r="J20" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="K20" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="K20" t="s" s="2">
+      <c r="L20" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="L20" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
@@ -4073,7 +4070,7 @@
         <v>73</v>
       </c>
       <c r="AE20" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AF20" t="s" s="2">
         <v>74</v>
@@ -4091,21 +4088,21 @@
         <v>73</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN20" t="s" s="2">
         <v>211</v>
-      </c>
-      <c r="AL20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM20" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>212</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B21" s="2"/>
       <c r="C21" t="s" s="2">
@@ -4128,16 +4125,16 @@
         <v>83</v>
       </c>
       <c r="J21" t="s" s="2">
+        <v>213</v>
+      </c>
+      <c r="K21" t="s" s="2">
         <v>214</v>
       </c>
-      <c r="K21" t="s" s="2">
+      <c r="L21" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="L21" t="s" s="2">
+      <c r="M21" t="s" s="2">
         <v>216</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>217</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" t="s" s="2">
@@ -4187,7 +4184,7 @@
         <v>73</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AF21" t="s" s="2">
         <v>74</v>
@@ -4205,21 +4202,21 @@
         <v>73</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM21" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN21" t="s" s="2">
         <v>219</v>
-      </c>
-      <c r="AL21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>220</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B22" s="2"/>
       <c r="C22" t="s" s="2">
@@ -4245,13 +4242,13 @@
         <v>102</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
@@ -4262,29 +4259,29 @@
         <v>73</v>
       </c>
       <c r="R22" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="X22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="S22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="X22" t="s" s="2">
+      <c r="Y22" t="s" s="2">
         <v>226</v>
       </c>
-      <c r="Y22" t="s" s="2">
-        <v>227</v>
-      </c>
       <c r="Z22" t="s" s="2">
         <v>73</v>
       </c>
@@ -4301,7 +4298,7 @@
         <v>73</v>
       </c>
       <c r="AE22" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="AF22" t="s" s="2">
         <v>82</v>
@@ -4316,24 +4313,24 @@
         <v>94</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>229</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>232</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B23" s="2"/>
       <c r="C23" t="s" s="2">
@@ -4356,13 +4353,13 @@
         <v>83</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>234</v>
-      </c>
-      <c r="L23" t="s" s="2">
-        <v>235</v>
       </c>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
@@ -4389,11 +4386,11 @@
         <v>73</v>
       </c>
       <c r="W23" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X23" s="2"/>
       <c r="Y23" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="Z23" t="s" s="2">
         <v>73</v>
@@ -4411,7 +4408,7 @@
         <v>73</v>
       </c>
       <c r="AE23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AF23" t="s" s="2">
         <v>74</v>
@@ -4429,7 +4426,7 @@
         <v>73</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>73</v>
@@ -4443,7 +4440,7 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B24" s="2"/>
       <c r="C24" t="s" s="2">
@@ -4466,13 +4463,13 @@
         <v>83</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>239</v>
-      </c>
-      <c r="L24" t="s" s="2">
-        <v>240</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4499,11 +4496,11 @@
         <v>73</v>
       </c>
       <c r="W24" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X24" s="2"/>
       <c r="Y24" t="s" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Z24" t="s" s="2">
         <v>73</v>
@@ -4521,7 +4518,7 @@
         <v>73</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>74</v>
@@ -4539,10 +4536,10 @@
         <v>73</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="AL24" t="s" s="2">
         <v>242</v>
-      </c>
-      <c r="AL24" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>73</v>
@@ -4553,7 +4550,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B25" s="2"/>
       <c r="C25" t="s" s="2">
@@ -4576,16 +4573,16 @@
         <v>83</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K25" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="L25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="L25" t="s" s="2">
+      <c r="M25" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="M25" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
@@ -4611,11 +4608,11 @@
         <v>73</v>
       </c>
       <c r="W25" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="X25" s="2"/>
       <c r="Y25" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="Z25" t="s" s="2">
         <v>73</v>
@@ -4633,7 +4630,7 @@
         <v>73</v>
       </c>
       <c r="AE25" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="AF25" t="s" s="2">
         <v>74</v>
@@ -4648,10 +4645,10 @@
         <v>94</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="AL25" t="s" s="2">
         <v>73</v>
@@ -4665,7 +4662,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B26" s="2"/>
       <c r="C26" t="s" s="2">
@@ -4688,13 +4685,13 @@
         <v>83</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="L26" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="M26" s="2"/>
       <c r="N26" s="2"/>
@@ -4725,7 +4722,7 @@
       </c>
       <c r="X26" s="2"/>
       <c r="Y26" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="Z26" t="s" s="2">
         <v>73</v>
@@ -4743,7 +4740,7 @@
         <v>73</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AF26" t="s" s="2">
         <v>74</v>
@@ -4761,13 +4758,13 @@
         <v>73</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>253</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>254</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>73</v>
@@ -4775,7 +4772,7 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B27" s="2"/>
       <c r="C27" t="s" s="2">
@@ -4798,13 +4795,13 @@
         <v>83</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>256</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>257</v>
-      </c>
-      <c r="L27" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="M27" s="2"/>
       <c r="N27" s="2"/>
@@ -4835,7 +4832,7 @@
       </c>
       <c r="X27" s="2"/>
       <c r="Y27" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="Z27" t="s" s="2">
         <v>73</v>
@@ -4853,7 +4850,7 @@
         <v>73</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="AF27" t="s" s="2">
         <v>74</v>
@@ -4871,21 +4868,21 @@
         <v>73</v>
       </c>
       <c r="AK27" t="s" s="2">
+        <v>259</v>
+      </c>
+      <c r="AL27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="AL27" t="s" s="2">
+      <c r="AM27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>261</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>262</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B28" s="2"/>
       <c r="C28" t="s" s="2">
@@ -4908,13 +4905,13 @@
         <v>73</v>
       </c>
       <c r="J28" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K28" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K28" t="s" s="2">
+      <c r="L28" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M28" s="2"/>
       <c r="N28" s="2"/>
@@ -4965,7 +4962,7 @@
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF28" t="s" s="2">
         <v>74</v>
@@ -4983,7 +4980,7 @@
         <v>73</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>73</v>
@@ -4997,11 +4994,11 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B29" s="2"/>
       <c r="C29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D29" s="2"/>
       <c r="E29" t="s" s="2">
@@ -5023,13 +5020,13 @@
         <v>127</v>
       </c>
       <c r="K29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L29" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L29" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M29" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
@@ -5070,7 +5067,7 @@
         <v>130</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC29" t="s" s="2">
         <v>73</v>
@@ -5079,7 +5076,7 @@
         <v>131</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>74</v>
@@ -5097,7 +5094,7 @@
         <v>73</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>73</v>
@@ -5111,7 +5108,7 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B30" s="2"/>
       <c r="C30" t="s" s="2">
@@ -5134,19 +5131,19 @@
         <v>83</v>
       </c>
       <c r="J30" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="K30" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="K30" t="s" s="2">
+      <c r="L30" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="L30" t="s" s="2">
+      <c r="M30" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
         <v>73</v>
@@ -5195,7 +5192,7 @@
         <v>73</v>
       </c>
       <c r="AE30" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="AF30" t="s" s="2">
         <v>74</v>
@@ -5213,21 +5210,21 @@
         <v>73</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>272</v>
-      </c>
-      <c r="AL30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM30" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>273</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B31" s="2"/>
       <c r="C31" t="s" s="2">
@@ -5250,13 +5247,13 @@
         <v>73</v>
       </c>
       <c r="J31" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K31" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K31" t="s" s="2">
+      <c r="L31" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L31" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M31" s="2"/>
       <c r="N31" s="2"/>
@@ -5307,7 +5304,7 @@
         <v>73</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF31" t="s" s="2">
         <v>74</v>
@@ -5325,7 +5322,7 @@
         <v>73</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>73</v>
@@ -5339,11 +5336,11 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B32" s="2"/>
       <c r="C32" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" t="s" s="2">
@@ -5365,13 +5362,13 @@
         <v>127</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L32" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L32" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M32" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
@@ -5412,7 +5409,7 @@
         <v>130</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="AC32" t="s" s="2">
         <v>73</v>
@@ -5421,7 +5418,7 @@
         <v>131</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF32" t="s" s="2">
         <v>74</v>
@@ -5439,7 +5436,7 @@
         <v>73</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>73</v>
@@ -5453,7 +5450,7 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B33" s="2"/>
       <c r="C33" t="s" s="2">
@@ -5479,16 +5476,16 @@
         <v>96</v>
       </c>
       <c r="K33" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="L33" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="L33" t="s" s="2">
+      <c r="M33" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="O33" t="s" s="2">
         <v>73</v>
@@ -5537,7 +5534,7 @@
         <v>73</v>
       </c>
       <c r="AE33" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AF33" t="s" s="2">
         <v>74</v>
@@ -5555,21 +5552,21 @@
         <v>73</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AL33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM33" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>283</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B34" s="2"/>
       <c r="C34" t="s" s="2">
@@ -5592,16 +5589,16 @@
         <v>83</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="L34" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="M34" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="M34" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" t="s" s="2">
@@ -5651,7 +5648,7 @@
         <v>73</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>74</v>
@@ -5669,21 +5666,21 @@
         <v>73</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>288</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B35" s="2"/>
       <c r="C35" t="s" s="2">
@@ -5709,14 +5706,14 @@
         <v>102</v>
       </c>
       <c r="K35" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="L35" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="L35" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="M35" s="2"/>
       <c r="N35" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="O35" t="s" s="2">
         <v>73</v>
@@ -5765,7 +5762,7 @@
         <v>73</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AF35" t="s" s="2">
         <v>74</v>
@@ -5783,21 +5780,21 @@
         <v>73</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AL35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AL35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>297</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B36" s="2"/>
       <c r="C36" t="s" s="2">
@@ -5820,17 +5817,17 @@
         <v>83</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="L36" t="s" s="2">
         <v>299</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="M36" s="2"/>
       <c r="N36" t="s" s="2">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="O36" t="s" s="2">
         <v>73</v>
@@ -5879,7 +5876,7 @@
         <v>73</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AF36" t="s" s="2">
         <v>74</v>
@@ -5897,21 +5894,21 @@
         <v>73</v>
       </c>
       <c r="AK36" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="AL36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="AL36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>304</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B37" s="2"/>
       <c r="C37" t="s" s="2">
@@ -5934,19 +5931,19 @@
         <v>83</v>
       </c>
       <c r="J37" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="K37" t="s" s="2">
         <v>306</v>
       </c>
-      <c r="K37" t="s" s="2">
+      <c r="L37" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>309</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>310</v>
       </c>
       <c r="O37" t="s" s="2">
         <v>73</v>
@@ -5995,7 +5992,7 @@
         <v>73</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>74</v>
@@ -6013,21 +6010,21 @@
         <v>73</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>312</v>
-      </c>
-      <c r="AL37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM37" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>313</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B38" s="2"/>
       <c r="C38" t="s" s="2">
@@ -6050,19 +6047,19 @@
         <v>83</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>315</v>
       </c>
-      <c r="L38" t="s" s="2">
+      <c r="M38" t="s" s="2">
         <v>316</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="O38" t="s" s="2">
         <v>73</v>
@@ -6111,7 +6108,7 @@
         <v>73</v>
       </c>
       <c r="AE38" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="AF38" t="s" s="2">
         <v>74</v>
@@ -6129,21 +6126,21 @@
         <v>73</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>320</v>
-      </c>
-      <c r="AL38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>321</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B39" s="2"/>
       <c r="C39" t="s" s="2">
@@ -6166,13 +6163,13 @@
         <v>83</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="M39" s="2"/>
       <c r="N39" s="2"/>
@@ -6202,11 +6199,11 @@
         <v>106</v>
       </c>
       <c r="X39" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="Y39" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="Y39" t="s" s="2">
-        <v>326</v>
-      </c>
       <c r="Z39" t="s" s="2">
         <v>73</v>
       </c>
@@ -6223,7 +6220,7 @@
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="AF39" t="s" s="2">
         <v>74</v>
@@ -6238,24 +6235,24 @@
         <v>94</v>
       </c>
       <c r="AJ39" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AK39" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="AK39" t="s" s="2">
+      <c r="AL39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN39" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>329</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B40" s="2"/>
       <c r="C40" t="s" s="2">
@@ -6278,13 +6275,13 @@
         <v>73</v>
       </c>
       <c r="J40" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="K40" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="K40" t="s" s="2">
+      <c r="L40" t="s" s="2">
         <v>332</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>333</v>
       </c>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
@@ -6335,7 +6332,7 @@
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>74</v>
@@ -6350,10 +6347,10 @@
         <v>94</v>
       </c>
       <c r="AJ40" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AK40" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>335</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>73</v>
@@ -6367,7 +6364,7 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B41" s="2"/>
       <c r="C41" t="s" s="2">
@@ -6390,16 +6387,16 @@
         <v>73</v>
       </c>
       <c r="J41" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="K41" t="s" s="2">
         <v>337</v>
       </c>
-      <c r="K41" t="s" s="2">
+      <c r="L41" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="L41" t="s" s="2">
+      <c r="M41" t="s" s="2">
         <v>339</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>340</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" t="s" s="2">
@@ -6449,7 +6446,7 @@
         <v>73</v>
       </c>
       <c r="AE41" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AF41" t="s" s="2">
         <v>74</v>
@@ -6464,24 +6461,24 @@
         <v>94</v>
       </c>
       <c r="AJ41" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="AK41" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AK41" t="s" s="2">
+      <c r="AL41" t="s" s="2">
         <v>342</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AM41" t="s" s="2">
+        <v>254</v>
+      </c>
+      <c r="AN41" t="s" s="2">
         <v>343</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>344</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B42" s="2"/>
       <c r="C42" t="s" s="2">
@@ -6504,13 +6501,13 @@
         <v>73</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K42" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="L42" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
@@ -6561,7 +6558,7 @@
         <v>73</v>
       </c>
       <c r="AE42" t="s" s="2">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="AF42" t="s" s="2">
         <v>74</v>
@@ -6579,21 +6576,21 @@
         <v>73</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="AL42" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AM42" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>349</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>350</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B43" s="2"/>
       <c r="C43" t="s" s="2">
@@ -6616,13 +6613,13 @@
         <v>73</v>
       </c>
       <c r="J43" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="K43" t="s" s="2">
+      <c r="L43" t="s" s="2">
         <v>353</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>354</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -6673,7 +6670,7 @@
         <v>73</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>74</v>
@@ -6688,16 +6685,16 @@
         <v>94</v>
       </c>
       <c r="AJ43" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="AK43" t="s" s="2">
         <v>355</v>
       </c>
-      <c r="AK43" t="s" s="2">
+      <c r="AL43" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AM43" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>73</v>
@@ -6705,7 +6702,7 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B44" s="2"/>
       <c r="C44" t="s" s="2">
@@ -6728,13 +6725,13 @@
         <v>83</v>
       </c>
       <c r="J44" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>360</v>
       </c>
-      <c r="K44" t="s" s="2">
+      <c r="L44" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -6785,7 +6782,7 @@
         <v>73</v>
       </c>
       <c r="AE44" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AF44" t="s" s="2">
         <v>74</v>
@@ -6800,24 +6797,24 @@
         <v>94</v>
       </c>
       <c r="AJ44" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AK44" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="AK44" t="s" s="2">
+      <c r="AL44" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AM44" t="s" s="2">
         <v>365</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>367</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B45" s="2"/>
       <c r="C45" t="s" s="2">
@@ -6840,13 +6837,13 @@
         <v>83</v>
       </c>
       <c r="J45" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="K45" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
@@ -6897,7 +6894,7 @@
         <v>73</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="AF45" t="s" s="2">
         <v>74</v>
@@ -6912,24 +6909,24 @@
         <v>94</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AL45" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AM45" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>374</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B46" s="2"/>
       <c r="C46" t="s" s="2">
@@ -6952,13 +6949,13 @@
         <v>73</v>
       </c>
       <c r="J46" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="K46" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="K46" t="s" s="2">
+      <c r="L46" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -7009,7 +7006,7 @@
         <v>73</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="AF46" t="s" s="2">
         <v>74</v>
@@ -7024,13 +7021,13 @@
         <v>94</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL46" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>73</v>
@@ -7041,7 +7038,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B47" s="2"/>
       <c r="C47" t="s" s="2">
@@ -7064,13 +7061,13 @@
         <v>73</v>
       </c>
       <c r="J47" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="K47" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="K47" t="s" s="2">
+      <c r="L47" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
@@ -7121,7 +7118,7 @@
         <v>73</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AF47" t="s" s="2">
         <v>74</v>
@@ -7139,7 +7136,7 @@
         <v>73</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>73</v>
@@ -7153,7 +7150,7 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B48" s="2"/>
       <c r="C48" t="s" s="2">
@@ -7176,16 +7173,16 @@
         <v>73</v>
       </c>
       <c r="J48" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="K48" t="s" s="2">
         <v>387</v>
       </c>
-      <c r="K48" t="s" s="2">
+      <c r="L48" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>390</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
@@ -7235,7 +7232,7 @@
         <v>73</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="AF48" t="s" s="2">
         <v>74</v>
@@ -7250,13 +7247,13 @@
         <v>94</v>
       </c>
       <c r="AJ48" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AK48" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AK48" t="s" s="2">
+      <c r="AL48" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="AL48" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>73</v>
@@ -7267,7 +7264,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B49" s="2"/>
       <c r="C49" t="s" s="2">
@@ -7290,16 +7287,16 @@
         <v>73</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K49" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="L49" t="s" s="2">
         <v>395</v>
       </c>
-      <c r="L49" t="s" s="2">
+      <c r="M49" t="s" s="2">
         <v>396</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>397</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
@@ -7349,7 +7346,7 @@
         <v>73</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>74</v>
@@ -7364,24 +7361,24 @@
         <v>94</v>
       </c>
       <c r="AJ49" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="AK49" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="AK49" t="s" s="2">
+      <c r="AL49" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL49" t="s" s="2">
-        <v>400</v>
-      </c>
       <c r="AM49" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="B50" s="2"/>
       <c r="C50" t="s" s="2">
@@ -7404,13 +7401,13 @@
         <v>73</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>402</v>
-      </c>
-      <c r="L50" t="s" s="2">
-        <v>403</v>
       </c>
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
@@ -7461,7 +7458,7 @@
         <v>73</v>
       </c>
       <c r="AE50" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AF50" t="s" s="2">
         <v>74</v>
@@ -7479,25 +7476,25 @@
         <v>73</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="B51" s="2"/>
       <c r="C51" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="D51" s="2"/>
       <c r="E51" t="s" s="2">
@@ -7516,13 +7513,13 @@
         <v>73</v>
       </c>
       <c r="J51" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>407</v>
       </c>
-      <c r="K51" t="s" s="2">
+      <c r="L51" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="L51" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="M51" s="2"/>
       <c r="N51" s="2"/>
@@ -7573,7 +7570,7 @@
         <v>73</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AF51" t="s" s="2">
         <v>74</v>
@@ -7588,10 +7585,10 @@
         <v>94</v>
       </c>
       <c r="AJ51" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AK51" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AK51" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>73</v>
@@ -7605,7 +7602,7 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B52" s="2"/>
       <c r="C52" t="s" s="2">
@@ -7628,13 +7625,13 @@
         <v>73</v>
       </c>
       <c r="J52" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="K52" t="s" s="2">
+      <c r="L52" t="s" s="2">
         <v>414</v>
-      </c>
-      <c r="L52" t="s" s="2">
-        <v>415</v>
       </c>
       <c r="M52" s="2"/>
       <c r="N52" s="2"/>
@@ -7685,7 +7682,7 @@
         <v>73</v>
       </c>
       <c r="AE52" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AF52" t="s" s="2">
         <v>82</v>
@@ -7697,27 +7694,27 @@
         <v>73</v>
       </c>
       <c r="AI52" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AJ52" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AJ52" t="s" s="2">
+      <c r="AK52" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AK52" t="s" s="2">
+      <c r="AL52" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AM52" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN52" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>420</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B53" s="2"/>
       <c r="C53" t="s" s="2">
@@ -7740,13 +7737,13 @@
         <v>73</v>
       </c>
       <c r="J53" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="K53" t="s" s="2">
+      <c r="L53" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="L53" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="M53" s="2"/>
       <c r="N53" s="2"/>
@@ -7797,7 +7794,7 @@
         <v>73</v>
       </c>
       <c r="AE53" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="AF53" t="s" s="2">
         <v>74</v>
@@ -7815,7 +7812,7 @@
         <v>73</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>73</v>
@@ -7829,11 +7826,11 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B54" s="2"/>
       <c r="C54" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D54" s="2"/>
       <c r="E54" t="s" s="2">
@@ -7855,13 +7852,13 @@
         <v>127</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L54" t="s" s="2">
-        <v>165</v>
-      </c>
       <c r="M54" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
@@ -7911,7 +7908,7 @@
         <v>73</v>
       </c>
       <c r="AE54" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AF54" t="s" s="2">
         <v>74</v>
@@ -7929,7 +7926,7 @@
         <v>73</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>73</v>
@@ -7943,11 +7940,11 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B55" s="2"/>
       <c r="C55" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D55" s="2"/>
       <c r="E55" t="s" s="2">
@@ -7969,16 +7966,16 @@
         <v>127</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="L55" t="s" s="2">
-        <v>426</v>
-      </c>
       <c r="M55" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>145</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>146</v>
       </c>
       <c r="O55" t="s" s="2">
         <v>73</v>
@@ -8027,7 +8024,7 @@
         <v>73</v>
       </c>
       <c r="AE55" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AF55" t="s" s="2">
         <v>74</v>
@@ -8059,7 +8056,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B56" s="2"/>
       <c r="C56" t="s" s="2">
@@ -8082,16 +8079,16 @@
         <v>83</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="K56" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="L56" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="L56" t="s" s="2">
+      <c r="M56" t="s" s="2">
         <v>430</v>
-      </c>
-      <c r="M56" t="s" s="2">
-        <v>431</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" t="s" s="2">
@@ -8117,14 +8114,14 @@
         <v>73</v>
       </c>
       <c r="W56" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X56" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="Y56" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="Y56" t="s" s="2">
-        <v>433</v>
-      </c>
       <c r="Z56" t="s" s="2">
         <v>73</v>
       </c>
@@ -8141,7 +8138,7 @@
         <v>73</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AF56" t="s" s="2">
         <v>74</v>
@@ -8159,21 +8156,21 @@
         <v>73</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AM56" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>434</v>
-      </c>
-      <c r="AL56" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN56" t="s" s="2">
-        <v>435</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B57" s="2"/>
       <c r="C57" t="s" s="2">
@@ -8196,13 +8193,13 @@
         <v>83</v>
       </c>
       <c r="J57" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="K57" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="K57" t="s" s="2">
+      <c r="L57" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="L57" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -8253,7 +8250,7 @@
         <v>73</v>
       </c>
       <c r="AE57" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AF57" t="s" s="2">
         <v>74</v>
@@ -8271,21 +8268,21 @@
         <v>73</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
         <v>441</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>443</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" t="s" s="2">
@@ -8311,10 +8308,10 @@
         <v>102</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="L58" t="s" s="2">
-        <v>446</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -8341,14 +8338,14 @@
         <v>73</v>
       </c>
       <c r="W58" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X58" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="Y58" t="s" s="2">
         <v>447</v>
       </c>
-      <c r="Y58" t="s" s="2">
-        <v>448</v>
-      </c>
       <c r="Z58" t="s" s="2">
         <v>73</v>
       </c>
@@ -8365,7 +8362,7 @@
         <v>73</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>74</v>
@@ -8383,10 +8380,10 @@
         <v>73</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AL58" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="AL58" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>73</v>
@@ -8397,7 +8394,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B59" s="2"/>
       <c r="C59" t="s" s="2">
@@ -8423,10 +8420,10 @@
         <v>102</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>452</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>453</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -8453,14 +8450,14 @@
         <v>73</v>
       </c>
       <c r="W59" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X59" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="Y59" t="s" s="2">
         <v>454</v>
       </c>
-      <c r="Y59" t="s" s="2">
-        <v>455</v>
-      </c>
       <c r="Z59" t="s" s="2">
         <v>73</v>
       </c>
@@ -8477,7 +8474,7 @@
         <v>73</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="AF59" t="s" s="2">
         <v>82</v>
@@ -8495,21 +8492,21 @@
         <v>73</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="AL59" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AM59" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN59" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="AM59" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>458</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B60" s="2"/>
       <c r="C60" t="s" s="2">
@@ -8532,13 +8529,13 @@
         <v>73</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="L60" t="s" s="2">
         <v>460</v>
-      </c>
-      <c r="L60" t="s" s="2">
-        <v>461</v>
       </c>
       <c r="M60" s="2"/>
       <c r="N60" s="2"/>
@@ -8589,7 +8586,7 @@
         <v>73</v>
       </c>
       <c r="AE60" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="AF60" t="s" s="2">
         <v>74</v>
@@ -8607,7 +8604,7 @@
         <v>73</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AL60" t="s" s="2">
         <v>73</v>
@@ -8621,7 +8618,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B61" s="2"/>
       <c r="C61" t="s" s="2">
@@ -8644,16 +8641,16 @@
         <v>73</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="K61" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="L61" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="L61" t="s" s="2">
+      <c r="M61" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="M61" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
@@ -8703,7 +8700,7 @@
         <v>73</v>
       </c>
       <c r="AE61" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="AF61" t="s" s="2">
         <v>74</v>
@@ -8718,19 +8715,19 @@
         <v>94</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="AK61" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="AL61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="AL61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>467</v>
       </c>
     </row>
   </sheetData>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-20T22:25:44+00:00</t>
+    <t>2023-02-21T14:23:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T14:23:26+00:00</t>
+    <t>2023-02-21T19:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-21T19:28:17+00:00</t>
+    <t>2023-02-22T15:40:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T15:40:59+00:00</t>
+    <t>2023-02-22T16:44:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T16:44:04+00:00</t>
+    <t>2023-02-22T20:35:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-22T20:35:25+00:00</t>
+    <t>2023-02-27T14:20:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T14:20:24+00:00</t>
+    <t>2023-02-27T15:22:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-02-27T15:22:20+00:00</t>
+    <t>2023-03-02T15:13:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T15:13:04+00:00</t>
+    <t>2023-03-02T20:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T20:01:22+00:00</t>
+    <t>2023-03-03T15:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-03T15:04:24+00:00</t>
+    <t>2023-03-06T14:18:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-06T14:18:09+00:00</t>
+    <t>2023-03-08T00:16:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:16:35+00:00</t>
+    <t>2023-03-08T00:32:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-08T00:32:01+00:00</t>
+    <t>2023-03-09T19:11:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1372,7 +1372,7 @@
     <t>Appointment.participant.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PractitionerRoleLE)
+    <t xml:space="preserve">Reference(http://minsal.cl/listaespera/StructureDefinition/PatientLE)
 </t>
   </si>
   <si>
@@ -7613,7 +7613,7 @@
         <v>82</v>
       </c>
       <c r="F52" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G52" t="s" s="2">
         <v>83</v>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:11:45+00:00</t>
+    <t>2023-03-09T19:22:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:22:45+00:00</t>
+    <t>2023-03-09T19:42:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-09T19:42:39+00:00</t>
+    <t>2023-03-10T17:11:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -6812,7 +6812,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="45" hidden="true">
+    <row r="45">
       <c r="A45" t="s" s="2">
         <v>367</v>
       </c>
@@ -6828,7 +6828,7 @@
         <v>82</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>73</v>
@@ -7148,7 +7148,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>385</v>
       </c>
@@ -7164,7 +7164,7 @@
         <v>82</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>73</v>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T17:11:36+00:00</t>
+    <t>2023-03-10T20:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
+++ b/refs/heads/master/StructureDefinition-AppointmentLE.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-10T20:13:24+00:00</t>
+    <t>2023-03-11T11:08:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
